--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486738_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486738_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8528</v>
+        <v>7.6748</v>
       </c>
       <c r="E2" t="n">
-        <v>8.292299999999999</v>
+        <v>8.188800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4395</v>
+        <v>-0.514</v>
       </c>
       <c r="G2" t="n">
         <v>6.1951</v>
@@ -610,13 +610,13 @@
         <v>0.5792</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7502</v>
+        <v>0.5723</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7443</v>
+        <v>0.6409</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0059</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.3282</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7961</v>
+        <v>4.7396</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9228</v>
+        <v>6.6677</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1267</v>
+        <v>-1.928</v>
       </c>
       <c r="G3" t="n">
         <v>4.2664</v>
@@ -688,13 +688,13 @@
         <v>0.7723</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1322</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6339</v>
+        <v>0.3789</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5017</v>
+        <v>-0.3031</v>
       </c>
       <c r="V3" t="n">
         <v>1.5559</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2959</v>
+        <v>4.1442</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9102</v>
+        <v>3.7586</v>
       </c>
       <c r="F4" t="n">
         <v>0.3856</v>
@@ -766,10 +766,10 @@
         <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1583</v>
+        <v>1.0067</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1581</v>
+        <v>1.0065</v>
       </c>
       <c r="U4" t="n">
         <v>0.0002</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9948</v>
+        <v>2.1042</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2144</v>
+        <v>2.3206</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2092</v>
+        <v>-0.2164</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2078</v>
+        <v>0.4545</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0618</v>
+        <v>-0.2553</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.2696</v>
+        <v>0.7098</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.4623</v>
+        <v>1.5317</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.317</v>
+        <v>1.1248</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.1452</v>
+        <v>0.4069</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2544</v>
+        <v>-1.0772</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3788</v>
+        <v>-1.3801</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1244</v>
+        <v>0.3029</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3958</v>
+        <v>0.3793</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0202</v>
+        <v>0.241</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3755</v>
+        <v>0.1384</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2277</v>
+        <v>1.2703</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2277</v>
+        <v>1.5133</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3168</v>
+        <v>1.2612</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3346</v>
+        <v>-0.7245</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0178</v>
+        <v>1.9857</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4545</v>
+        <v>-1.2078</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2553</v>
+        <v>1.0618</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7098</v>
+        <v>-2.2696</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5317</v>
+        <v>-2.4623</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1248</v>
+        <v>-0.317</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4069</v>
+        <v>-2.1452</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0772</v>
+        <v>1.2544</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3801</v>
+        <v>1.3788</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3029</v>
+        <v>-0.1244</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.408</v>
+        <v>0.6621</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.745</v>
+        <v>0.51</v>
       </c>
       <c r="U6" t="n">
-        <v>0.337</v>
+        <v>0.152</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2703</v>
+        <v>1.2277</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5133</v>
+        <v>1.2277</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.451</v>
+        <v>0.8427</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3053</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1457</v>
+        <v>0.2202</v>
       </c>
       <c r="G7" t="n">
         <v>1.7084</v>
@@ -1000,13 +1000,13 @@
         <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6123</v>
+        <v>-0.2206</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3587</v>
+        <v>-0.0415</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2535</v>
+        <v>-0.179</v>
       </c>
       <c r="V7" t="n">
         <v>0.8995</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0612</v>
+        <v>0.5411</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6001</v>
+        <v>1.1794</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.539</v>
+        <v>-0.6383</v>
       </c>
       <c r="G8" t="n">
         <v>0.3301</v>
@@ -1078,13 +1078,13 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5625</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.745</v>
+        <v>-0.1658</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1825</v>
+        <v>0.0832</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2856</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1497</v>
+        <v>-0.1248</v>
       </c>
       <c r="E9" t="n">
         <v>0.0407</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1904</v>
+        <v>-0.1655</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1662</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5406</v>
+        <v>-0.4358</v>
       </c>
       <c r="E10" t="n">
-        <v>0.523</v>
+        <v>0.5782</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0636</v>
+        <v>-1.0139</v>
       </c>
       <c r="G10" t="n">
         <v>0.2884</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2152</v>
+        <v>-0.1103</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1104</v>
+        <v>-0.0552</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1048</v>
+        <v>-0.0551</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6138</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0408</v>
+        <v>-0.7801</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0894</v>
+        <v>-1.0272</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0485</v>
+        <v>0.2472</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4729</v>
@@ -1312,13 +1312,13 @@
         <v>0.9654</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1158</v>
+        <v>0.145</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0004</v>
+        <v>0.0618</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1155</v>
+        <v>0.0832</v>
       </c>
       <c r="V11" t="n">
         <v>1.5133</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6874</v>
+        <v>-2.7894</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6088</v>
+        <v>-1.7605</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0785</v>
+        <v>-1.0289</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8158</v>
@@ -1390,13 +1390,13 @@
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0221</v>
+        <v>-0.1241</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4684</v>
+        <v>0.3167</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4905</v>
+        <v>-0.4408</v>
       </c>
       <c r="V12" t="n">
         <v>-0.0426</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3501</v>
+        <v>17.1777</v>
       </c>
       <c r="E13" t="n">
-        <v>19.0164</v>
+        <v>19.8443</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6665</v>
+        <v>-2.6663</v>
       </c>
       <c r="G13" t="n">
         <v>11.1731</v>
@@ -1465,22 +1465,22 @@
         <v>-7.723199999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>6.757700000000001</v>
+        <v>6.7577</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5172</v>
+        <v>2.345</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0654</v>
+        <v>2.8933</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5483</v>
+        <v>-0.5482</v>
       </c>
       <c r="V13" t="n">
         <v>4.6252</v>
       </c>
       <c r="W13" t="n">
-        <v>8.180299999999999</v>
+        <v>8.180300000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-3.5551</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0061</v>
+        <v>1.9483</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1356</v>
+        <v>3.4116</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1295</v>
+        <v>-1.4634</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9441000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6992</v>
+        <v>0.6413</v>
       </c>
       <c r="T14" t="n">
-        <v>1.351</v>
+        <v>0.627</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3482</v>
+        <v>0.0143</v>
       </c>
       <c r="V14" t="n">
         <v>0.8995</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9225</v>
+        <v>1.0276</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1527</v>
+        <v>3.8082</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.2301</v>
+        <v>-2.7805</v>
       </c>
       <c r="G15" t="n">
         <v>0.3149</v>
@@ -1624,13 +1624,13 @@
         <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9358</v>
+        <v>1.041</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9853</v>
+        <v>0.6408</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0494</v>
+        <v>0.4002</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3282</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1034</v>
+        <v>0.5834</v>
       </c>
       <c r="E16" t="n">
-        <v>1.874</v>
+        <v>2.0808</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7706</v>
+        <v>-1.4975</v>
       </c>
       <c r="G16" t="n">
         <v>0.625</v>
@@ -1702,13 +1702,13 @@
         <v>0.9654</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2594</v>
+        <v>0.2206</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5238</v>
+        <v>0.7307</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7832</v>
+        <v>-0.51</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2277</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. VIVANCOS ORTIZ</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2248</v>
+        <v>-0.9809</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2808</v>
+        <v>0.8988</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.944</v>
+        <v>-1.8797</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.0678</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.883</v>
+        <v>3.2757</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1809</v>
+        <v>-3.3435</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3814</v>
+        <v>2.2852</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1929</v>
+        <v>3.6211</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5743</v>
+        <v>-1.336</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0835</v>
+        <v>-2.353</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6901</v>
+        <v>-0.3454</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3934</v>
+        <v>-2.0075</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4302</v>
+        <v>0.3379</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6622</v>
+        <v>0.5444</v>
       </c>
       <c r="U17" t="n">
-        <v>0.232</v>
+        <v>-0.2065</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2856</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>E. VIVANCOS ORTIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2899</v>
+        <v>-1.2359</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9635</v>
+        <v>-0.2808</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2534</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.6125</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.7443</v>
+        <v>-0.883</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8682</v>
+        <v>0.1809</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5976</v>
+        <v>0.3814</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.33</v>
+        <v>-0.1929</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7325</v>
+        <v>0.5743</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0149</v>
+        <v>-1.0835</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4143</v>
+        <v>-0.6901</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6006</v>
+        <v>-0.3934</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4577</v>
+        <v>-0.4413</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0477</v>
+        <v>-0.6622</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.59</v>
+        <v>0.2209</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8995</v>
+        <v>-0.2856</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6138</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8373</v>
+        <v>-1.2444</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.032</v>
+        <v>0.8601</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8052</v>
+        <v>-2.1044</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0678</v>
+        <v>-3.6125</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2757</v>
+        <v>-2.7443</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.3435</v>
+        <v>-0.8682</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2852</v>
+        <v>-1.5976</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6211</v>
+        <v>-2.33</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.336</v>
+        <v>0.7325</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.353</v>
+        <v>-2.0149</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3454</v>
+        <v>-0.4143</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0075</v>
+        <v>-1.6006</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9654</v>
+        <v>0.9654</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5184</v>
+        <v>0.5033</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3864</v>
+        <v>0.9443</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.132</v>
+        <v>-0.441</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2856</v>
+        <v>0.8995</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2856</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9186</v>
+        <v>-1.5242</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.986</v>
+        <v>-1.7791</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0674</v>
+        <v>0.2549</v>
       </c>
       <c r="G20" t="n">
         <v>-0.545</v>
@@ -2014,13 +2014,13 @@
         <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7944</v>
+        <v>-0.4</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3311</v>
+        <v>-0.1242</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4633</v>
+        <v>-0.2757</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1175</v>
+        <v>-2.4899</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6283</v>
+        <v>-1.5248</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4892</v>
+        <v>-0.9651</v>
       </c>
       <c r="G21" t="n">
         <v>0.2397</v>
@@ -2092,13 +2092,13 @@
         <v>0.5792</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4344</v>
+        <v>-0.8068</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8829</v>
+        <v>-0.7795</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5515</v>
+        <v>-0.0274</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5712</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2561</v>
+        <v>-2.6037</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0718</v>
+        <v>-1.9684</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1843</v>
+        <v>-0.6354</v>
       </c>
       <c r="G22" t="n">
         <v>-1.761</v>
@@ -2170,13 +2170,13 @@
         <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4178</v>
+        <v>-0.7655</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9381</v>
+        <v>-0.8347</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4797</v>
+        <v>0.0692</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6565</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8484</v>
+        <v>-3.5133</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.972</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8763</v>
+        <v>-2.8515</v>
       </c>
       <c r="G23" t="n">
         <v>-2.324</v>
@@ -2248,13 +2248,13 @@
         <v>0.1931</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2042</v>
+        <v>0.1309</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2759</v>
+        <v>0.0344</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0717</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5133</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8895</v>
+        <v>-4.938</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4885</v>
+        <v>-2.1782</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.401</v>
+        <v>-2.7598</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3962</v>
@@ -2326,13 +2326,13 @@
         <v>0.5792</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5512</v>
+        <v>-0.5997</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8829</v>
+        <v>-0.5726</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3317</v>
+        <v>-0.0271</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5559</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-16.3501</v>
+        <v>-14.971</v>
       </c>
       <c r="E25" t="n">
         <v>2.666399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-19.0162</v>
+        <v>-17.6375</v>
       </c>
       <c r="G25" t="n">
         <v>-11.1731</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7232</v>
+        <v>-1.723199999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-9.449700000000002</v>
@@ -2380,7 +2380,7 @@
         <v>5.320600000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>4.144699999999999</v>
+        <v>4.1447</v>
       </c>
       <c r="L25" t="n">
         <v>1.176</v>
@@ -2404,13 +2404,13 @@
         <v>7.723100000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5173</v>
+        <v>-0.1382999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5483</v>
+        <v>0.5484000000000004</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.0655</v>
+        <v>-0.6865</v>
       </c>
       <c r="V25" t="n">
         <v>-4.625000000000001</v>
